--- a/nmoreau/ig/ValueSet-preadmission-consent-purpose-reason-vs.xlsx
+++ b/nmoreau/ig/ValueSet-preadmission-consent-purpose-reason-vs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="39">
   <si>
     <t>Property</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Finalités du traitement dans le cadre des consentements</t>
+    <t>preadmission-consent-purpose-reason-vs</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T09:00:47+00:00</t>
+    <t>2025-05-22T16:12:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -108,10 +108,19 @@
     <t>TREAT</t>
   </si>
   <si>
-    <t>CAREMGT</t>
-  </si>
-  <si>
-    <t>INFORMATION</t>
+    <t>Treatment</t>
+  </si>
+  <si>
+    <t>PATREQ</t>
+  </si>
+  <si>
+    <t>Patient Request</t>
+  </si>
+  <si>
+    <t>HMO</t>
+  </si>
+  <si>
+    <t>Healthcare Operations</t>
   </si>
   <si>
     <t/>
@@ -411,34 +420,40 @@
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" t="s" s="2">
+        <v>31</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" s="2"/>
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>33</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" s="2"/>
+        <v>34</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>35</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/nmoreau/ig/ValueSet-preadmission-consent-purpose-reason-vs.xlsx
+++ b/nmoreau/ig/ValueSet-preadmission-consent-purpose-reason-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-22T16:12:30+00:00</t>
+    <t>2025-05-26T06:59:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/ValueSet-preadmission-consent-purpose-reason-vs.xlsx
+++ b/nmoreau/ig/ValueSet-preadmission-consent-purpose-reason-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-26T06:59:47+00:00</t>
+    <t>2025-06-02T15:02:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/ValueSet-preadmission-consent-purpose-reason-vs.xlsx
+++ b/nmoreau/ig/ValueSet-preadmission-consent-purpose-reason-vs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="37">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-02T15:02:23+00:00</t>
+    <t>2025-10-22T09:09:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -115,12 +115,6 @@
   </si>
   <si>
     <t>Patient Request</t>
-  </si>
-  <si>
-    <t>HMO</t>
-  </si>
-  <si>
-    <t>Healthcare Operations</t>
   </si>
   <si>
     <t/>
@@ -401,7 +395,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -437,23 +431,15 @@
         <v>34</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B5" t="s" s="2">
         <v>36</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/nmoreau/ig/ValueSet-preadmission-consent-purpose-reason-vs.xlsx
+++ b/nmoreau/ig/ValueSet-preadmission-consent-purpose-reason-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-22T09:09:51+00:00</t>
+    <t>2025-10-28T10:00:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/ValueSet-preadmission-consent-purpose-reason-vs.xlsx
+++ b/nmoreau/ig/ValueSet-preadmission-consent-purpose-reason-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-28T10:00:18+00:00</t>
+    <t>2025-11-19T09:47:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/ValueSet-preadmission-consent-purpose-reason-vs.xlsx
+++ b/nmoreau/ig/ValueSet-preadmission-consent-purpose-reason-vs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-19T09:47:12+00:00</t>
+    <t>2026-01-14T12:51:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/ValueSet-preadmission-consent-purpose-reason-vs.xlsx
+++ b/nmoreau/ig/ValueSet-preadmission-consent-purpose-reason-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-14T12:51:21+00:00</t>
+    <t>2026-02-24T09:27:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/ValueSet-preadmission-consent-purpose-reason-vs.xlsx
+++ b/nmoreau/ig/ValueSet-preadmission-consent-purpose-reason-vs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>1.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T09:27:09+00:00</t>
+    <t>2026-04-10T11:37:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
